--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/FLORIDA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/FLORIDA_2016.xlsx
@@ -1687,7 +1687,7 @@
         <v>25</v>
       </c>
       <c r="D74">
-        <v>0.0009721952167995333</v>
+        <v>0.0009721952167995332</v>
       </c>
     </row>
     <row r="75">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C159">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C211">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C352">
@@ -8545,7 +8545,7 @@
         <v>25</v>
       </c>
       <c r="D455">
-        <v>0.0009721952167995333</v>
+        <v>0.0009721952167995332</v>
       </c>
     </row>
     <row r="456">
@@ -8977,7 +8977,7 @@
         <v>25</v>
       </c>
       <c r="D479">
-        <v>0.0009721952167995333</v>
+        <v>0.0009721952167995332</v>
       </c>
     </row>
     <row r="480">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C793">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C936">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 26-</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C937">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C996">
@@ -20947,7 +20947,7 @@
         <v>25</v>
       </c>
       <c r="D1144">
-        <v>0.0009721952167995333</v>
+        <v>0.0009721952167995332</v>
       </c>
     </row>
     <row r="1145">
@@ -24439,7 +24439,7 @@
         <v>25</v>
       </c>
       <c r="D1338">
-        <v>0.0009721952167995333</v>
+        <v>0.0009721952167995332</v>
       </c>
     </row>
     <row r="1339">
@@ -28633,7 +28633,7 @@
         <v>25</v>
       </c>
       <c r="D1571">
-        <v>0.0009721952167995333</v>
+        <v>0.0009721952167995332</v>
       </c>
     </row>
     <row r="1572">
